--- a/src/attributions/attributions_ig_traj_495.xlsx
+++ b/src/attributions/attributions_ig_traj_495.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,19 +1002,19 @@
         <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1135635860823204</v>
+        <v>0.1087702871845012</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2627613492971648</v>
+        <v>0.1379137685476333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01347081606661644</v>
+        <v>-0.08532339660845453</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1023,22 +1023,22 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.02265144341177558</v>
+        <v>0.02276217945924276</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2387385148544099</v>
+        <v>-0.03108129521705379</v>
       </c>
       <c r="N2" t="n">
-        <v>0.005719642659729415</v>
+        <v>-0.02110561529883775</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -1047,193 +1047,193 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1083997172967939</v>
+        <v>0.05377705462845132</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01236818953665744</v>
+        <v>-0.1003784459453512</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.04361436512658663</v>
+        <v>0.109981832930831</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.07833672262594704</v>
+        <v>-0.01806079046887585</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01171560210610239</v>
+        <v>0.03705762658817776</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.009298368432744866</v>
+        <v>-0.0485313875974238</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.04486821589741342</v>
+        <v>0.1616159992480079</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03216264382969419</v>
+        <v>-0.02746355535896297</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07941566810152632</v>
+        <v>0.2473418400382405</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1587414854446407</v>
+        <v>0.3383634728292114</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09496770416775556</v>
+        <v>-0.02790017531855319</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01841125536205374</v>
+        <v>0.05118523459194756</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02837554453630514</v>
+        <v>-0.1261252015591958</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.09823586953220728</v>
+        <v>0.04432085640514877</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03785559630282209</v>
+        <v>-0.1303142086922739</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03083793472071189</v>
+        <v>-0.07391993463497157</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.03925015716482984</v>
+        <v>-0.09881889896373287</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.09536144570456224</v>
+        <v>-0.03819146859333423</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.03912296556476491</v>
+        <v>0.1452122959808533</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02213707306184231</v>
+        <v>-0.1546110400108008</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.01990996932938572</v>
+        <v>0.009924116663328366</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,52 +1245,52 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03053216949848069</v>
+        <v>-0.1375875779526713</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.04036857196174517</v>
+        <v>-0.05615664651927584</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01834765950112722</v>
+        <v>-0.02183254655870858</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01776595600963329</v>
+        <v>-0.1122868210558121</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.03678342491833134</v>
+        <v>0.1837800491855179</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.04830583973100779</v>
+        <v>0.004044890293164284</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
@@ -1299,19 +1299,19 @@
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04587107387803037</v>
+        <v>-0.1382358447668215</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04331952876540518</v>
+        <v>-0.05026160940242464</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.009187832693228098</v>
+        <v>0.004166871868126827</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1323,49 +1323,49 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03492830179516355</v>
+        <v>-0.09711963147491562</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01594690992218723</v>
+        <v>0.08566694662263544</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03940935874805038</v>
+        <v>-0.007971256534051308</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.03807029712088379</v>
+        <v>0.01816036835845185</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04801233879067612</v>
+        <v>-0.05471439633673748</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.02779739109799752</v>
+        <v>0.006021978199299319</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,52 +1377,52 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.07018650623358692</v>
+        <v>0.007599294295473997</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.01311686632312821</v>
+        <v>0.1625848788128795</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03947747523715595</v>
+        <v>0.2783402438402429</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04817555933695059</v>
+        <v>-0.1248474077373729</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0908645092385791</v>
+        <v>0.1786878788944629</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.03158698639538209</v>
+        <v>0.0305806724569631</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04351795522603605</v>
+        <v>-0.09863649735078135</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.03605048602120684</v>
+        <v>0.01497159799810562</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01943489707753068</v>
+        <v>0.005272153588648468</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04032481743670978</v>
+        <v>-0.1776723507274474</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.0337791203645583</v>
+        <v>-0.01313043223818898</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01881023979325147</v>
+        <v>-0.01419925687467011</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1482,73 +1482,73 @@
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.004887850227421824</v>
+        <v>-0.1874829865980238</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.0157778721620328</v>
+        <v>-0.04511234036853715</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.008101020542556516</v>
+        <v>0.1268029727241752</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.00516732990964021</v>
+        <v>-0.1595881896761019</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.008857138002429203</v>
+        <v>0.2174693646033881</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.0141670900926394</v>
+        <v>-0.0742829398717323</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.04489119929027677</v>
+        <v>-0.04786247361951582</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02588855511003614</v>
+        <v>-0.01378282087949264</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,214 +1568,214 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.04464873915373078</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01187220919489511</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.04991590241607061</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.01807855316078502</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.003555083256680507</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.01171205473404913</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.03634064181160786</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.03672529836555192</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.02934848905597705</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.00515568777955889</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.02904544650797774</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.04351032457176483</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0.0004692608558169037</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.06135887511796423</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.01272666049803516</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.0247607363488937</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.0753191763881581</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.05534751026204433</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.01540900650733368</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.04935785858577198</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.004775121909268794</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.03851814551021304</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.06530154133389637</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.001448796112852864</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1784,25 +1784,25 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.002382119183789797</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.03374926683588599</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.02669033588642237</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.02828562536233062</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
@@ -1820,25 +1820,25 @@
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.02718059873066673</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.02135270116193398</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.002331877641132263</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.06690001155613244</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.02351967143957178</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.02394654118120858</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.03944858157140008</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.03173846586500534</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,52 +1892,52 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.003391599793005596</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.04456702598762777</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.008524985386910038</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01469971378391758</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.03406111062754647</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.01563252426430185</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,37 +1946,37 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0.005795072539302709</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.03121801614292953</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.06422544377938512</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.02544010263988801</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.01743387827630686</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.007655686798862048</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.0167552195655094</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.05229213630224329</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.006820173441392647</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.03522248030576124</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,99 +2039,6927 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.04613265907598669</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.03311990639381886</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.02158949604590116</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.03041326445684275</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.007595843095332489</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.006166663830881094</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.04355942397807732</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.02490204034999449</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.003834608963664209</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.03035617329602876</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4430125302526361</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0645578664656376</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3398139108549774</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2357540941522222</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.03051396841850568</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.06494288916083724</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.139649070791309</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.1197149661408791</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1371154936059689</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1140753475684942</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.03930883127546358</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1099469974366495</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1293479851575225</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.008580630680122788</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2282172282879618</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6876316001510808</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2749746616247674</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.3848108443931438</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1387341607760451</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.0585482857089963</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.163538086790338</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.04904547466459945</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.142326887684899</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1456046273784007</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2384562666164688</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.09680811219146221</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.2737278669795493</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2836739063781173</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.04359772407984543</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1851595465332024</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.3796532879632407</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.06809764450423482</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.2107042141209962</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2666959506152169</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.03673250285827095</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1539220926236999</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.1227243040925306</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.06277706518635336</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.118000482072227</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.1034383219392685</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.00321736310038318</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.04566234043017453</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.141394570584908</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.04606314194597713</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.123678373035829</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.12932173451761</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.07309954666875036</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.1734880167502444</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1736853137108331</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.179435227447715</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2037596041997894</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2635509976661128</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.09901471720057051</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1637202720365402</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.152541724987043</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.03105879377994606</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2346787020016208</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.01217007546924355</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.02483667922750218</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.07620885674469703</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.1224186706038769</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1270199865015474</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5172929532855178</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07400504989951268</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2719261039271875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2877326738336139</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.03297740210157681</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.2095817292526398</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1649789032407412</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1485694950374103</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.02538269483004115</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.01456851205524754</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.3165265786654279</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.01373753646116316</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2007448710771286</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1195192388319551</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1269600671336445</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.8594901310680707</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1721322909480879</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.194334821812549</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.02131602719531331</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.06922221513812173</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1701616759318622</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.04676907716963147</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.1204754523182428</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1261913462733744</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.409251029553057</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.01112513174279849</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.2632332621964094</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.2523602010998909</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.06075494057407334</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1955314277586987</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.2513879007310719</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.07837372925245571</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.01199587133914072</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.2349427434706419</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.05229166673297368</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.2125109483897739</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.04557832431211713</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.1535205392438865</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.05178188581232947</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.1072925615150948</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.02207547354439277</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.0079555275394556</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.03883251519401437</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.01706170973868604</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.1644429222115214</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.07014091504943788</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.131505107243684</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.0672893244904693</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.1475389776515383</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.1753172988700878</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.07157468530166888</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.2612930997232103</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.09630839941675091</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1819474905543397</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.2455317596044117</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.05960831586086754</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.265561435086981</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.02795538821500648</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.004100205658343806</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.1243736624306785</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.1033095632252573</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1180568458155078</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5078737701096502</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.03231355489667083</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2781230044938222</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3512811557028319</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.04716127566377983</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1959805337214431</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1501526082866059</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1652824064795556</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.03120379580889946</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.08272950706646419</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.3063110097970588</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.1211795751237854</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1990896635623257</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1192374362497603</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1372984491760067</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.7269127886730475</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.2263797686715476</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.2280537115007013</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.01011249045673466</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.08762083034707646</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.2429262379939461</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.02872729903786493</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.1048719469971237</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.04899445372159072</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3591097505243385</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.04953258130066918</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.1696373797346885</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2492259386238816</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.03643127671756288</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1683549629718956</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.2627060561691598</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1340908377218782</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.0650083534257114</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.231505980053201</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.04909145171831598</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.167047000601622</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.06256743356794119</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.06597119518934765</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.003385849019958357</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.08177843282788003</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.05893265601272497</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.1314363581163073</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.04506770260029933</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1357720880637305</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.1026375500284701</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.07843193804952391</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.07335219889870316</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.06353134666080217</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.1077619917668914</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.08408078104056252</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1574002579877688</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2622359202875769</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.07107925286353811</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1357257498696233</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.3175042685462208</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.1148250551594187</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2835829368336283</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.04737369058200714</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.002144164512728056</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.134266284813659</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.04901336092090171</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.03717183723639256</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5086490032850663</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1086445295805512</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.03445744187583723</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1009098187875747</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4570281494881004</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1733440982399181</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.09902039199914262</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.04489536878205466</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1098613889067056</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1154812195189388</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1120098622848756</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.003434995465204126</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.008395595638852508</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.2580236043768015</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.1796713223762981</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.06020771962411704</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2122877515154919</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.06802569908100976</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.07517868793545564</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.16179789617253</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.5766764437141431</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.008140557656261463</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.2491339029869285</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1294632692248445</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.03966236233420154</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.1461557835268148</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.07641758622759552</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.04389247224596916</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.04372540216882714</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.03238279338254316</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1367332415297522</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.004464566752622579</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2902113764383825</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.05336517326388283</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.06513473785783963</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.09919240707121196</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.1966212700833288</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07203111330186744</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.03295994957665298</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.03932126661902756</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1592504924175125</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1318124805359009</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.143026142144533</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0839544312025378</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1701425093502825</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.06775780047148265</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.02355773403678052</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.03940675446075859</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.02019924582745648</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.004258234586761787</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.2911629333440506</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0.004463719045018637</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.1222886287956799</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.002969330865924711</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.05536941684267969</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.06208692222135494</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.1067228432455755</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.01446156812393495</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.05245666922094822</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.05469849481213791</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06788006137846775</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.09137730451300208</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.02098312094402096</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.004959340340845393</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.07496524023881816</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.01276210771266206</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02500500432290998</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.1297160762675563</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.2102828550147989</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.06468613988112858</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.01734327464113096</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.02277419362327915</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.09273170729977624</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.1075649389675708</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.01822101241918108</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.1269733750773368</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1791455544849057</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.2700587777651017</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.008147571586729451</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.07883943791327983</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1329799420375362</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.07750317944018514</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.02470208543346421</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.2818564398151195</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.04162056370787673</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2882330872168639</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1851611210173689</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.04016557515846494</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1953527119332352</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.104339569155418</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.008342206693918051</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.02828669988393097</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.02245632528317229</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.181707428522615</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.0557535531195088</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1094977770562122</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.09786536045502911</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1581088807862863</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.3217771429857014</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.0787483414600899</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1578030382418962</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.08262864260019186</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.1962964246293518</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1394668135353883</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.01656339895258239</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.05728509787336127</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.0440201852941423</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.2110265858516741</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.003325655409296704</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.09955459620676631</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1234209859023821</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.00648914440585495</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.09600565947186977</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1218531426167358</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.2065042241469998</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.08017272205657189</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.117364047715709</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.002737856853797861</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.0948763065855644</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.00183868947560469</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.07621596710591608</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.008320133182171891</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.01033207326630372</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.0382639630535861</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.0254960303962508</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.001832385681207095</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.04545088872768778</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>-0.00297905068392372</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.04668484576333822</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.02223637454769818</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>-0.02161288428114111</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1135890106286803</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.08030162980747192</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.1145122597007558</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1355344253752506</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.004919031825858098</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.0769986010642885</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1596455949142274</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.04855051237715004</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.1044543464523749</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1408587392878429</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.008442769093517247</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.07489993244536318</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.08279986811722487</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.01168330730609188</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4743058118961426</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.03041211803169411</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1938641756850119</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.554685684516999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.07651280952905998</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1296098380392814</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.09843139265759417</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01841314098432351</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.07581865861895451</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.0009011620215169627</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.09953429812047901</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.04198586707496138</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1339510928089198</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.05844269470513321</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.07737985433109675</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.5501184157344312</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2252649136116192</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.197240727909066</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1624159325060212</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.0009239793828838863</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.01742888428210865</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.02321156441889962</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.06037907507364074</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.01927685977225841</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.335198288840461</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.006098966362624466</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.1057035698934457</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1846366316670197</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.01113018036215179</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.061294613025353</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.08639373284798427</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.1079261660902333</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.04818360217450846</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1778101860912086</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.009033146014415903</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.07026058243130388</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.008511385456063954</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.01223933783442321</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.06567880017663522</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.08606641174405262</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.04025390934387472</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.08911412123862585</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.1126595431646772</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.04445581357759502</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.09317822523377196</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.1016056184315871</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.04487812578086018</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.0125598314668814</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.06293073616362913</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.006717079594241213</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.05726367121530131</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2020405123587581</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.004570544228444403</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.07655425098209344</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.1004678554741948</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.02268407687261526</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.05337571470500857</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.161672157985384</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.05273811549810577</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.0060432158339664</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1071531546563514</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.03567341988381507</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.5101255040792251</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1811703883228331</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.03863166987721699</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.5974404689424635</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3180072649287298</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.09155247522863946</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.04979308967113324</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01299248413502367</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.006843271780366956</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.04986561842864165</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.192369428904383</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.3004840446951947</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1741947203233778</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.04945848713120329</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.254971730120328</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.2618305467327942</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1829076594844744</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.02675566565566078</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.02861470252620437</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.004007197441668412</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.1290132630798923</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1154663531941085</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.1314360106627933</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.001949711247084899</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.1912799971632666</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.07752362218927715</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.01320465216038244</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.2165927942735979</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.07313905081879743</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.02704847286581574</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.1245455317878508</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.1388355243929686</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.08036871305366554</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.2217869458134953</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.07134494161584672</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.004757497195584303</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1528146541787375</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.02743238480922545</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.004995428131004643</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.05206061711792918</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0.09105068895215733</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.08850249782816044</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.05641490302349154</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.03844670365203098</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.006379464581282528</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.2532852896959757</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.04693744995211887</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.0225571607240555</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.1415737802073747</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.01326612883567985</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.01981114260946812</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.2514237789134706</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0.08983736668808509</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.02988211804639379</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1101997747421716</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.115369136342948</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.07656895062206241</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.2532762728308344</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.01264050806171984</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.07817485013265829</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.2149178774957931</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0.007445269660772184</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3690567145681935</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.03921435834006509</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1590863430653323</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4832250748441802</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.132804229446824</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.2286465199943702</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.09558652204727792</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1109951814929264</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.005621405988054011</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.02913897464484006</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2622975299803364</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.004135101336126799</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.02744147505064875</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.03850598968769738</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.01927863060349114</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.4339746446479105</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2475429448205427</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.1021483513894079</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.007382856655655217</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.01912174129215596</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.07038815455052266</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.05422531642102469</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.07605603669584898</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.02679177562219323</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.2350165428718404</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.07251311061429468</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.09058216440086625</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.09897639290146362</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.02892350128137651</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.04972868158234884</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.1447614207192784</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1318269874237873</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.1083160640611046</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1015389607716618</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.0112002678045713</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.06930023191677602</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.04971322258341543</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1628632728990317</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.0418488563439199</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.00938030508301861</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.05216832893454001</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.06698126895401929</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.006468406858750855</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.08641849994074217</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.03691247623482077</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.04052379350961152</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.02475796686636171</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.003264693534635761</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.01171106393125514</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.0076212217173049</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1123028590268153</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1190437166368356</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.00178958399266416</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.03998146389230554</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1881406343935356</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.1012019943061498</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1089599617102297</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.008758165312516449</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.02639772784504632</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.04082168554232907</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.02961442177430135</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.06374967201989523</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
         <v>0</v>
       </c>
     </row>
